--- a/Aug_2026/daily Reports/LMT Orders.xlsx
+++ b/Aug_2026/daily Reports/LMT Orders.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18CF405-BAF1-4A28-9561-569268310099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BD62A9-846D-4005-9212-BDF3A9AACE64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1848,6 +1848,42 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1885,42 +1921,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2485,14 +2485,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B1" s="176">
+      <c r="B1" s="163">
         <f ca="1">TODAY()</f>
-        <v>46268</v>
-      </c>
-      <c r="C1" s="176"/>
-      <c r="D1" s="176"/>
-      <c r="E1" s="176"/>
-      <c r="F1" s="176"/>
+        <v>46279</v>
+      </c>
+      <c r="C1" s="163"/>
+      <c r="D1" s="163"/>
+      <c r="E1" s="163"/>
+      <c r="F1" s="163"/>
       <c r="G1" s="10"/>
       <c r="H1" s="10"/>
       <c r="I1" s="10"/>
@@ -2514,10 +2514,10 @@
       <c r="Y1" s="10"/>
     </row>
     <row r="2" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="173" t="s">
+      <c r="A2" s="185" t="s">
         <v>37</v>
       </c>
-      <c r="B2" s="177" t="s">
+      <c r="B2" s="164" t="s">
         <v>12</v>
       </c>
       <c r="C2" s="12" t="s">
@@ -2550,13 +2550,13 @@
       <c r="L2" s="15">
         <v>120</v>
       </c>
-      <c r="M2" s="165"/>
-      <c r="N2" s="166"/>
-      <c r="O2" s="167"/>
-      <c r="P2" s="168" t="s">
+      <c r="M2" s="177"/>
+      <c r="N2" s="178"/>
+      <c r="O2" s="179"/>
+      <c r="P2" s="180" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="169"/>
+      <c r="Q2" s="181"/>
       <c r="R2" s="18">
         <v>0.05</v>
       </c>
@@ -2575,8 +2575,8 @@
       <c r="Y2" s="20"/>
     </row>
     <row r="3" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="173"/>
-      <c r="B3" s="178"/>
+      <c r="A3" s="185"/>
+      <c r="B3" s="165"/>
       <c r="C3" s="23" t="s">
         <v>15</v>
       </c>
@@ -2607,29 +2607,29 @@
       <c r="L3" s="29">
         <v>72.64</v>
       </c>
-      <c r="M3" s="170" t="s">
+      <c r="M3" s="182" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="171"/>
-      <c r="O3" s="172"/>
+      <c r="N3" s="183"/>
+      <c r="O3" s="184"/>
       <c r="P3" s="71"/>
       <c r="Q3" s="72"/>
-      <c r="R3" s="180" t="s">
+      <c r="R3" s="167" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="181"/>
-      <c r="T3" s="181"/>
-      <c r="U3" s="182"/>
-      <c r="V3" s="183" t="s">
+      <c r="S3" s="168"/>
+      <c r="T3" s="168"/>
+      <c r="U3" s="169"/>
+      <c r="V3" s="170" t="s">
         <v>17</v>
       </c>
-      <c r="W3" s="184"/>
-      <c r="X3" s="184"/>
-      <c r="Y3" s="185"/>
+      <c r="W3" s="171"/>
+      <c r="X3" s="171"/>
+      <c r="Y3" s="172"/>
     </row>
     <row r="4" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="173"/>
-      <c r="B4" s="179"/>
+      <c r="A4" s="185"/>
+      <c r="B4" s="166"/>
       <c r="C4" s="30" t="s">
         <v>18</v>
       </c>
@@ -12452,10 +12452,10 @@
     </row>
     <row r="133" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A133" s="78"/>
-      <c r="B133" s="186" t="s">
+      <c r="B133" s="173" t="s">
         <v>11</v>
       </c>
-      <c r="C133" s="187"/>
+      <c r="C133" s="174"/>
       <c r="D133" s="84">
         <f t="shared" ref="D133:L133" si="111">SUM(D6:D61)</f>
         <v>6363</v>
@@ -12719,10 +12719,10 @@
       </c>
     </row>
     <row r="137" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B137" s="174" t="s">
+      <c r="B137" s="186" t="s">
         <v>70</v>
       </c>
-      <c r="C137" s="175"/>
+      <c r="C137" s="187"/>
       <c r="D137" s="83">
         <f>SUM(D135:D136)</f>
         <v>0</v>
@@ -12813,10 +12813,10 @@
       </c>
     </row>
     <row r="138" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="B138" s="163" t="s">
+      <c r="B138" s="175" t="s">
         <v>11</v>
       </c>
-      <c r="C138" s="164"/>
+      <c r="C138" s="176"/>
       <c r="D138" s="85">
         <f>SUM(D133,D137)</f>
         <v>6363</v>
@@ -12908,17 +12908,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="R3:U3"/>
-    <mergeCell ref="V3:Y3"/>
-    <mergeCell ref="B133:C133"/>
     <mergeCell ref="B138:C138"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="M3:O3"/>
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B137:C137"/>
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="R3:U3"/>
+    <mergeCell ref="V3:Y3"/>
+    <mergeCell ref="B133:C133"/>
   </mergeCells>
   <conditionalFormatting sqref="C46:C60">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
